--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8498,6 +8498,54 @@
         <v>342.59</v>
       </c>
       <c r="F336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="C337" t="n">
+        <v>322.42</v>
+      </c>
+      <c r="D337" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="E337" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>323.96</v>
+      </c>
+      <c r="C338" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="D338" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="E338" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="F338" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8514,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11997,6 +12045,26 @@
       </c>
       <c r="B348" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -12165,28 +12233,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1436294022047174</v>
+        <v>0.1416181384409202</v>
       </c>
       <c r="J2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07070636171985434</v>
+        <v>0.06963489906905684</v>
       </c>
       <c r="M2" t="n">
-        <v>2.96498467152642</v>
+        <v>2.956365762194209</v>
       </c>
       <c r="N2" t="n">
-        <v>14.54374809864081</v>
+        <v>14.47477534057533</v>
       </c>
       <c r="O2" t="n">
-        <v>3.813626633355815</v>
+        <v>3.804572951143838</v>
       </c>
       <c r="P2" t="n">
-        <v>322.1982569881118</v>
+        <v>322.2193594780109</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12243,28 +12311,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1404576058371391</v>
+        <v>0.1390417558672248</v>
       </c>
       <c r="J3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05190136296369741</v>
+        <v>0.05152281081165477</v>
       </c>
       <c r="M3" t="n">
-        <v>3.329578361813414</v>
+        <v>3.316263500198773</v>
       </c>
       <c r="N3" t="n">
-        <v>19.33127267688766</v>
+        <v>19.22495971605305</v>
       </c>
       <c r="O3" t="n">
-        <v>4.39673431957034</v>
+        <v>4.384627659910594</v>
       </c>
       <c r="P3" t="n">
-        <v>320.0696774665134</v>
+        <v>320.0845305471756</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12321,28 +12389,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1468183254340222</v>
+        <v>0.1428748391985707</v>
       </c>
       <c r="J4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06464531390991346</v>
+        <v>0.06195684467064544</v>
       </c>
       <c r="M4" t="n">
-        <v>3.137889292831383</v>
+        <v>3.135119961293187</v>
       </c>
       <c r="N4" t="n">
-        <v>16.72996278830146</v>
+        <v>16.69523915818383</v>
       </c>
       <c r="O4" t="n">
-        <v>4.090227718391906</v>
+        <v>4.085980807368511</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1231379630947</v>
+        <v>325.1645111096572</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12399,28 +12467,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07970070808337763</v>
+        <v>0.07945487312025405</v>
       </c>
       <c r="J5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02157828969959563</v>
+        <v>0.02172130322702892</v>
       </c>
       <c r="M5" t="n">
-        <v>2.962248897108251</v>
+        <v>2.946529655721648</v>
       </c>
       <c r="N5" t="n">
-        <v>15.45000362089606</v>
+        <v>15.35908710827334</v>
       </c>
       <c r="O5" t="n">
-        <v>3.930649262004442</v>
+        <v>3.919067122195452</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5633903946877</v>
+        <v>342.5659712857594</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12458,7 +12526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23213,6 +23281,70 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-35.45950446736462,174.43307327147502</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-35.46016495992601,174.43346115461847</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-35.46080189292436,174.43390411114422</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-35.461374463064395,174.43449754492548</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-35.45950714017455,174.4330670220629</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-35.460163748803005,174.4334639864021</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-35.46080368873794,174.43389991226692</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-35.461376927109214,174.43449178364958</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8548,6 +8548,30 @@
       <c r="F338" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>322.76</v>
+      </c>
+      <c r="C339" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="D339" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="E339" t="n">
+        <v>344.28</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12065,6 +12089,16 @@
       </c>
       <c r="B350" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -12233,28 +12267,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1416181384409202</v>
+        <v>0.1397262126647572</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06963489906905684</v>
+        <v>0.06819066592944434</v>
       </c>
       <c r="M2" t="n">
-        <v>2.956365762194209</v>
+        <v>2.955974448638353</v>
       </c>
       <c r="N2" t="n">
-        <v>14.47477534057533</v>
+        <v>14.46188326168092</v>
       </c>
       <c r="O2" t="n">
-        <v>3.804572951143838</v>
+        <v>3.802878286466833</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2193594780109</v>
+        <v>322.2392746878088</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12311,28 +12345,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1390417558672248</v>
+        <v>0.1384404295010579</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05152281081165477</v>
+        <v>0.0514073747873397</v>
       </c>
       <c r="M3" t="n">
-        <v>3.316263500198773</v>
+        <v>3.309160799905304</v>
       </c>
       <c r="N3" t="n">
-        <v>19.22495971605305</v>
+        <v>19.1711049727877</v>
       </c>
       <c r="O3" t="n">
-        <v>4.384627659910594</v>
+        <v>4.378482039792752</v>
       </c>
       <c r="P3" t="n">
-        <v>320.0845305471756</v>
+        <v>320.0908603624834</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12389,28 +12423,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1428748391985707</v>
+        <v>0.1406933032609877</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06195684467064544</v>
+        <v>0.06042312393572313</v>
       </c>
       <c r="M4" t="n">
-        <v>3.135119961293187</v>
+        <v>3.134655205499124</v>
       </c>
       <c r="N4" t="n">
-        <v>16.69523915818383</v>
+        <v>16.68564306978461</v>
       </c>
       <c r="O4" t="n">
-        <v>4.085980807368511</v>
+        <v>4.084806368701535</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1645111096572</v>
+        <v>325.1874748783346</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12467,28 +12501,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07945487312025405</v>
+        <v>0.07923152450230699</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02172130322702892</v>
+        <v>0.02173839864353311</v>
       </c>
       <c r="M5" t="n">
-        <v>2.946529655721648</v>
+        <v>2.93900298707662</v>
       </c>
       <c r="N5" t="n">
-        <v>15.35908710827334</v>
+        <v>15.31406318367945</v>
       </c>
       <c r="O5" t="n">
-        <v>3.919067122195452</v>
+        <v>3.913318691811267</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5659712857594</v>
+        <v>342.5683223476459</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12526,7 +12560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23345,6 +23379,38 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-35.4595121516923,174.43305530441398</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-35.46016362351441,174.43346427934523</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-35.46080452400003,174.43389795930068</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-35.4613764259476,174.43449295543454</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8572,6 +8572,30 @@
       <c r="F339" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="C340" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="D340" t="n">
+        <v>325.58</v>
+      </c>
+      <c r="E340" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12099,6 +12123,16 @@
       </c>
       <c r="B351" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -12267,28 +12301,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1397262126647572</v>
+        <v>0.1362796621445209</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06819066592944434</v>
+        <v>0.06509646320926288</v>
       </c>
       <c r="M2" t="n">
-        <v>2.955974448638353</v>
+        <v>2.962089436566691</v>
       </c>
       <c r="N2" t="n">
-        <v>14.46188326168092</v>
+        <v>14.5143322850589</v>
       </c>
       <c r="O2" t="n">
-        <v>3.802878286466833</v>
+        <v>3.809768009348981</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2392746878088</v>
+        <v>322.2760608993242</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12345,28 +12379,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1384404295010579</v>
+        <v>0.1371773037557809</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0514073747873397</v>
+        <v>0.05081441357229921</v>
       </c>
       <c r="M3" t="n">
-        <v>3.309160799905304</v>
+        <v>3.304896074599895</v>
       </c>
       <c r="N3" t="n">
-        <v>19.1711049727877</v>
+        <v>19.12732764712834</v>
       </c>
       <c r="O3" t="n">
-        <v>4.378482039792752</v>
+        <v>4.373480038496614</v>
       </c>
       <c r="P3" t="n">
-        <v>320.0908603624834</v>
+        <v>320.1043421352193</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12423,28 +12457,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1406933032609877</v>
+        <v>0.1386601772741622</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06042312393572313</v>
+        <v>0.05905673278595291</v>
       </c>
       <c r="M4" t="n">
-        <v>3.134655205499124</v>
+        <v>3.133313600400759</v>
       </c>
       <c r="N4" t="n">
-        <v>16.68564306978461</v>
+        <v>16.66951944988942</v>
       </c>
       <c r="O4" t="n">
-        <v>4.084806368701535</v>
+        <v>4.082832282850891</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1874748783346</v>
+        <v>325.2091751267859</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12501,28 +12535,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07923152450230699</v>
+        <v>0.07949985644850575</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02173839864353311</v>
+        <v>0.02202729383172053</v>
       </c>
       <c r="M5" t="n">
-        <v>2.93900298707662</v>
+        <v>2.931543971426506</v>
       </c>
       <c r="N5" t="n">
-        <v>15.31406318367945</v>
+        <v>15.26946545573839</v>
       </c>
       <c r="O5" t="n">
-        <v>3.913318691811267</v>
+        <v>3.907616339373454</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5683223476459</v>
+        <v>342.5654583490852</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12560,7 +12594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23411,6 +23445,38 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.459522592350744,174.43303089264066</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.46016796685181,174.4334541239829</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.460803145817586,174.43390118169495</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-35.46137287605233,174.43450125557757</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8596,6 +8596,54 @@
       <c r="F340" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>320.79</v>
+      </c>
+      <c r="C341" t="n">
+        <v>321.46</v>
+      </c>
+      <c r="D341" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="E341" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>325.49</v>
+      </c>
+      <c r="C342" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="D342" t="n">
+        <v>328.02</v>
+      </c>
+      <c r="E342" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12133,6 +12181,26 @@
       </c>
       <c r="B352" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -12301,28 +12369,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1362796621445209</v>
+        <v>0.1329512297829788</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06509646320926288</v>
+        <v>0.06263078485197482</v>
       </c>
       <c r="M2" t="n">
-        <v>2.962089436566691</v>
+        <v>2.959412302481733</v>
       </c>
       <c r="N2" t="n">
-        <v>14.5143322850589</v>
+        <v>14.50619541570286</v>
       </c>
       <c r="O2" t="n">
-        <v>3.809768009348981</v>
+        <v>3.808699963990714</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2760608993242</v>
+        <v>322.3117154256767</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12379,28 +12447,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1371773037557809</v>
+        <v>0.1343647523350053</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05081441357229921</v>
+        <v>0.04940660132027996</v>
       </c>
       <c r="M3" t="n">
-        <v>3.304896074599895</v>
+        <v>3.297776652787308</v>
       </c>
       <c r="N3" t="n">
-        <v>19.12732764712834</v>
+        <v>19.04699640026947</v>
       </c>
       <c r="O3" t="n">
-        <v>4.373480038496614</v>
+        <v>4.364286470921618</v>
       </c>
       <c r="P3" t="n">
-        <v>320.1043421352193</v>
+        <v>320.1344820705312</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12457,28 +12525,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1386601772741622</v>
+        <v>0.1353856482423229</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05905673278595291</v>
+        <v>0.05697645602243195</v>
       </c>
       <c r="M4" t="n">
-        <v>3.133313600400759</v>
+        <v>3.127568067207842</v>
       </c>
       <c r="N4" t="n">
-        <v>16.66951944988942</v>
+        <v>16.63482875429706</v>
       </c>
       <c r="O4" t="n">
-        <v>4.082832282850891</v>
+        <v>4.078581708669947</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2091751267859</v>
+        <v>325.2442549334473</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12535,28 +12603,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07949985644850575</v>
+        <v>0.08067072825817184</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02202729383172053</v>
+        <v>0.02293366904619232</v>
       </c>
       <c r="M5" t="n">
-        <v>2.931543971426506</v>
+        <v>2.924069653053247</v>
       </c>
       <c r="N5" t="n">
-        <v>15.26946545573839</v>
+        <v>15.20296990451535</v>
       </c>
       <c r="O5" t="n">
-        <v>3.907616339373454</v>
+        <v>3.89909860153797</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5654583490852</v>
+        <v>342.5529011525</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12594,7 +12662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23477,6 +23545,70 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.45952037893156,174.4330360679371</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.46016896916032,174.43345178043757</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.46080832444212,174.4338890733038</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-35.46137784590553,174.43448963537713</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.4595007504878,174.43308196206308</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.46016921973745,174.43345119455122</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.460792955617435,174.43392500787942</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-35.461363395741124,174.43452342183826</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
